--- a/Caleb_territory_chart.xlsx
+++ b/Caleb_territory_chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caleb\OneDrive\Documents\DATA_Labs\Capstone_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ca02095870d75e/Documents/DATA_Labs/Capstone_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8005F6-9AC0-4504-9CFE-47B1F3C19982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{5030F73E-9E97-42F3-A66E-7E7218BC528A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B9894451-3BB5-49D5-9703-F49DBFFE989E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B9894451-3BB5-49D5-9703-F49DBFFE989E}"/>
   </bookViews>
   <sheets>
     <sheet name="Caleb_territory_chart" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="64">
   <si>
     <t>SalesManager</t>
   </si>
@@ -224,7 +224,13 @@
     <t>Sum of Monthly_Revenue</t>
   </si>
   <si>
-    <t>S</t>
+    <t>This chart shows that total revenue have a consistence improvemeint over time</t>
+  </si>
+  <si>
+    <t>From 2022 through 2025, with 2025 making the greatest part of the total revenue</t>
+  </si>
+  <si>
+    <t>this indicate better growth in  Colorado over time</t>
   </si>
 </sst>
 </file>
@@ -232,9 +238,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,6 +371,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -713,12 +726,14 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -766,7 +781,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -800,6 +815,38 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Annual Revenue Distrebution For Colorado</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1268,6 +1315,35 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Annual</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Revenue Distrebution For Colorado</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1355,6 +1431,96 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1386,6 +1552,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-467D-4B97-82BE-D3B0968ECC85}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1399,6 +1570,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-467D-4B97-82BE-D3B0968ECC85}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1412,6 +1588,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-467D-4B97-82BE-D3B0968ECC85}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1425,6 +1606,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-467D-4B97-82BE-D3B0968ECC85}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2763,7 +2949,7 @@
     <cacheField name="Territory" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Sales_Month" numFmtId="165">
+    <cacheField name="Sales_Month" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2022-01-01T00:00:00" maxDate="2025-12-02T00:00:00" count="48">
         <d v="2022-01-01T00:00:00"/>
         <d v="2022-02-01T00:00:00"/>
@@ -3135,12 +3321,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9535113-D86A-42DB-844E-48B43208653B}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9535113-D86A-42DB-844E-48B43208653B}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0">
+    <pivotField numFmtId="164" showAll="0">
       <items count="49">
         <item x="0"/>
         <item x="1"/>
@@ -3256,12 +3442,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8578150-912B-430F-AD7E-B4502D1E6CD8}" name="PivotTable5" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8578150-912B-430F-AD7E-B4502D1E6CD8}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="165" showAll="0">
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
       <items count="49">
         <item x="0"/>
         <item x="1"/>
@@ -3353,12 +3539,60 @@
   <dataFields count="1">
     <dataField name="Sum of Monthly_Revenue" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="5">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -5107,74 +5341,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B467FF79-6CC9-4DB5-94D5-568BCF531C8A}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1011355.5199999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1487890.72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1491467.8099999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2421918.1700000004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="4">
-        <v>6412632.2200000007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{896C8DF5-B284-44A1-8478-AA3126D55123}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5194,7 +5360,7 @@
       <c r="A2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>1011355.5199999999</v>
       </c>
     </row>
@@ -5202,7 +5368,7 @@
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>1487890.72</v>
       </c>
     </row>
@@ -5210,7 +5376,7 @@
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>1491467.8099999998</v>
       </c>
     </row>
@@ -5218,7 +5384,7 @@
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>2421918.1700000004</v>
       </c>
     </row>
@@ -5226,7 +5392,7 @@
       <c r="A6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>6412632.2200000007</v>
       </c>
     </row>
@@ -5234,4 +5400,114 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{896C8DF5-B284-44A1-8478-AA3126D55123}">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2">
+        <v>1011355.5199999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3">
+        <v>1487890.72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4">
+        <v>1491467.8099999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5">
+        <v>2421918.1700000004</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>6412632.2200000007</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H5:O6"/>
+    <mergeCell ref="H8:O8"/>
+    <mergeCell ref="H7:O7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>